--- a/ejemplos/nomina-pago.xlsx
+++ b/ejemplos/nomina-pago.xlsx
@@ -165,7 +165,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>1570949</v>
+        <v>1571463</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
